--- a/data/trans_orig/IP16A09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A09-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25181</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28595</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25547</t>
+          <t>25456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52425</t>
+          <t>52639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57594</t>
+          <t>57596</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37723</t>
+          <t>37962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42703</t>
+          <t>42585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47707</t>
+          <t>47686</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87873</t>
+          <t>87703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93139</t>
+          <t>93148</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20264</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42400</t>
+          <t>42085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35528</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65535</t>
+          <t>65505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116111</t>
+          <t>115866</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123039</t>
+          <t>122929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136135</t>
+          <t>136723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142627</t>
+          <t>142631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254878</t>
+          <t>255652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>264326</t>
+          <t>264403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43589</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48355</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45653</t>
+          <t>45257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51117</t>
+          <t>51119</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92427</t>
+          <t>92530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99316</t>
+          <t>98973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60078</t>
+          <t>59136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69853</t>
+          <t>69498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131591</t>
+          <t>132205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138988</t>
+          <t>139112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>92</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28005</t>
+          <t>27539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62088</t>
+          <t>62639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67118</t>
+          <t>67632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178321</t>
+          <t>179419</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185854</t>
+          <t>185759</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180873</t>
+          <t>180978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188838</t>
+          <t>188985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>363259</t>
+          <t>363658</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373367</t>
+          <t>373604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28193</t>
+          <t>27727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59105</t>
+          <t>58698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>47057</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94554</t>
+          <t>94505</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36355</t>
+          <t>35744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42102</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>79697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85999</t>
+          <t>86000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33912</t>
+          <t>33414</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60466</t>
+          <t>61050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157406</t>
+          <t>156684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161969</t>
+          <t>161966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>141737</t>
+          <t>141108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147422</t>
+          <t>147418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>301701</t>
+          <t>300782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308416</t>
+          <t>308270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A09-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A09-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4040</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,62%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1562</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4395</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4169</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4199</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28320</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25615</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>27473</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24640</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28586</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24866</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28591</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,62%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28320</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25456</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,5%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52639</t>
+          <t>52437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57596</t>
+          <t>57648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3452</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2315</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3274</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50313</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47508</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>40906</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37962</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42585</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>37786</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42627</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>50313</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>47686</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87703</t>
+          <t>87551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93148</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1413,102 +1413,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2310</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3266</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4157</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4288</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23219</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20975</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>21980</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20197</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20228</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>89,88%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23219</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20600</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,29%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>67</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42085</t>
+          <t>42216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3918</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4396</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>14,39%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3579</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4443</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1435</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4476</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38796</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36213</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>29750</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>26625</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>26147</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,4%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>85,61%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38796</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35859</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>90,93%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>102</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65505</t>
+          <t>65538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7416</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5197</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9439</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2528</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>9976</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,15%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7196</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>140647</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136503</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>142637</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>120108</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>115866</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>122929</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>115329</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>122777</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,85%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>140647</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136723</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>142631</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255652</t>
+          <t>255911</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>264403</t>
+          <t>264678</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2674,67 +2674,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2267</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6242</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1771</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4789</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4920</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2267</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6492</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49482</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45507</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51125</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>47085</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44067</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48353</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43936</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48364</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,38%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>49482</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45257</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51119</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92530</t>
+          <t>91902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98973</t>
+          <t>99007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>48856</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>48856</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>48856</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51749</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51749</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51749</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3017,67 +3017,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5040</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1730</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6111</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5476</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5173</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73255</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69631</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>63517</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>59136</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>59771</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>91,61%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>73255</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>69498</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>193</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132205</t>
+          <t>132242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139112</t>
+          <t>139138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3468,47 +3468,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>37728</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,92 +3698,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4641</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1899</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5024</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>15,43%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1899</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30664</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27922</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31970</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35161</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>30664</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>27539</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>31964</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>84,57%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,16%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>96</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62639</t>
+          <t>62609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67632</t>
+          <t>67126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10721</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7573</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2493</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>10500</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>185896</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>180757</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>188867</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>183491</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>179419</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>185759</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>179223</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>185725</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,13%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>185896</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>180978</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>188985</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>363658</t>
+          <t>363026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>373604</t>
+          <t>373364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3566</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3440</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3513</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30680</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>27727</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27853</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,01%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>98</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58698</t>
+          <t>59077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1124</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4043</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3911</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3877</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1124</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3961</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>49976</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47057</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>47189</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>51100</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>92,35%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>147</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94505</t>
+          <t>94589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51100</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51100</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51100</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,92 +5302,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6360</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2799</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7056</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>704</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>40001</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>36440</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42098</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>43903</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>40001</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>35744</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>42094</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,46%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>83,51%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>119</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79697</t>
+          <t>79635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86000</t>
+          <t>85999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>540</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2906</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2231</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35699</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33414</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33333</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>36239</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,51%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>91,98%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>88</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61050</t>
+          <t>60376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5993,67 +5993,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>2277</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5852</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>145326</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>141204</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147420</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>160259</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>156684</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>161966</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>156588</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>161965</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>145326</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>141108</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>147418</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>452</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300782</t>
+          <t>300894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308270</t>
+          <t>308356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
